--- a/NSO_regions.xlsx
+++ b/NSO_regions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5DD4B1-E579-4FA1-A98D-3AE5FCBB0DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D28C13E-10EE-4D56-8D0B-69910126E612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
@@ -330,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -356,6 +356,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1042,8 +1045,8 @@
       <c r="G12" s="4">
         <v>6</v>
       </c>
-      <c r="H12" s="6">
-        <v>81.5</v>
+      <c r="H12" s="11">
+        <v>79.5</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>48</v>
@@ -1104,8 +1107,8 @@
       <c r="G14" s="4">
         <v>9</v>
       </c>
-      <c r="H14" s="6">
-        <v>89</v>
+      <c r="H14" s="11">
+        <v>84.3</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>50</v>
@@ -1135,8 +1138,8 @@
       <c r="G15" s="4">
         <v>4.8999999999999995</v>
       </c>
-      <c r="H15" s="6">
-        <v>87.9</v>
+      <c r="H15" s="11">
+        <v>80.599999999999994</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>51</v>
@@ -1228,8 +1231,8 @@
       <c r="G18" s="4">
         <v>4.8</v>
       </c>
-      <c r="H18" s="6">
-        <v>86.5</v>
+      <c r="H18" s="11">
+        <v>84.4</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>54</v>
@@ -1414,8 +1417,8 @@
       <c r="G24" s="4">
         <v>10</v>
       </c>
-      <c r="H24" s="6">
-        <v>79</v>
+      <c r="H24" s="11">
+        <v>68.2</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>60</v>

--- a/NSO_regions.xlsx
+++ b/NSO_regions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D28C13E-10EE-4D56-8D0B-69910126E612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5DD4B1-E579-4FA1-A98D-3AE5FCBB0DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
@@ -330,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -356,9 +356,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1045,8 +1042,8 @@
       <c r="G12" s="4">
         <v>6</v>
       </c>
-      <c r="H12" s="11">
-        <v>79.5</v>
+      <c r="H12" s="6">
+        <v>81.5</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>48</v>
@@ -1107,8 +1104,8 @@
       <c r="G14" s="4">
         <v>9</v>
       </c>
-      <c r="H14" s="11">
-        <v>84.3</v>
+      <c r="H14" s="6">
+        <v>89</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>50</v>
@@ -1138,8 +1135,8 @@
       <c r="G15" s="4">
         <v>4.8999999999999995</v>
       </c>
-      <c r="H15" s="11">
-        <v>80.599999999999994</v>
+      <c r="H15" s="6">
+        <v>87.9</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>51</v>
@@ -1231,8 +1228,8 @@
       <c r="G18" s="4">
         <v>4.8</v>
       </c>
-      <c r="H18" s="11">
-        <v>84.4</v>
+      <c r="H18" s="6">
+        <v>86.5</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>54</v>
@@ -1417,8 +1414,8 @@
       <c r="G24" s="4">
         <v>10</v>
       </c>
-      <c r="H24" s="11">
-        <v>68.2</v>
+      <c r="H24" s="6">
+        <v>79</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>60</v>

--- a/NSO_regions.xlsx
+++ b/NSO_regions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5DD4B1-E579-4FA1-A98D-3AE5FCBB0DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF8A052-D5E6-448A-AFEE-60B0DEA64B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
+    <workbookView xWindow="1452" yWindow="1452" windowWidth="23631" windowHeight="12542" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист2" sheetId="1" r:id="rId1"/>
@@ -1099,7 +1099,7 @@
         <v>401</v>
       </c>
       <c r="F14" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="4">
         <v>9</v>
@@ -1133,10 +1133,10 @@
         <v>2</v>
       </c>
       <c r="G15" s="4">
-        <v>4.8999999999999995</v>
+        <v>11.3</v>
       </c>
       <c r="H15" s="6">
-        <v>87.9</v>
+        <v>91.9</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>51</v>
@@ -1229,7 +1229,7 @@
         <v>4.8</v>
       </c>
       <c r="H18" s="6">
-        <v>86.5</v>
+        <v>86.7</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>54</v>
